--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/bilgi_sayfasi.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/bilgi_sayfasi.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bilgi Sayfası" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,16 +17,16 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="&quot;: &quot;#,##0.00\ &quot;saat &quot;"/>
-    <numFmt numFmtId="165" formatCode="&quot;: &quot;#,##0\ &quot;KİŞİ &quot;"/>
-    <numFmt numFmtId="166" formatCode="&quot;: &quot;#,##0\ &quot;lt/kişi.gün &quot;"/>
-    <numFmt numFmtId="167" formatCode="&quot;: &quot;#,##0\ &quot;gr/kişi.gün&quot;"/>
-    <numFmt numFmtId="168" formatCode="&quot;: &quot;#,##0\ &quot;m³/gün &quot;"/>
-    <numFmt numFmtId="169" formatCode="&quot;: &quot;#,##0\ &quot;m³/day &quot;"/>
-    <numFmt numFmtId="170" formatCode="&quot;: &quot;#,##0.00\ &quot;kg/day &quot;"/>
-    <numFmt numFmtId="171" formatCode="&quot;: &quot;#,##0\ &quot;PE &quot;"/>
-    <numFmt numFmtId="172" formatCode="&quot;: &quot;#,##0\ &quot;°C &quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot;: &quot;#,##0\ &quot;°C &quot;"/>
+    <numFmt numFmtId="166" formatCode="&quot;: &quot;#,##0\ &quot;KİŞİ &quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;: &quot;#,##0\ &quot;lt/kişi.gün &quot;"/>
+    <numFmt numFmtId="168" formatCode="&quot;: &quot;#,##0\ &quot;gr/kişi.gün&quot;"/>
+    <numFmt numFmtId="169" formatCode="&quot;: &quot;#,##0\ &quot;m³/gün &quot;"/>
+    <numFmt numFmtId="170" formatCode="&quot;: &quot;#,##0\ &quot;m³/day &quot;"/>
+    <numFmt numFmtId="171" formatCode="&quot;: &quot;#,##0.00\ &quot;kg/day &quot;"/>
+    <numFmt numFmtId="172" formatCode="&quot;: &quot;#,##0\ &quot;PE &quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,25 +67,45 @@
       <charset val="162"/>
       <family val="2"/>
       <b val="1"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <sz val="12"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="162"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
+      <b val="1"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="162"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
-      <sz val="14"/>
+      <color theme="1"/>
+      <sz val="10"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -213,74 +233,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -291,8 +274,88 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -659,291 +722,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="17.21875" customWidth="1" style="23" min="1" max="1"/>
-    <col width="68" customWidth="1" style="23" min="2" max="2"/>
-    <col width="59.109375" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="17.21875" customWidth="1" style="14" min="1" max="1"/>
+    <col width="68" customWidth="1" style="14" min="2" max="2"/>
+    <col width="59.109375" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.6" customHeight="1" s="23" thickTop="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>Acme Endüstri A.Ş.</t>
-        </is>
-      </c>
-      <c r="B1" s="29" t="n"/>
-      <c r="C1" s="30" t="n"/>
-    </row>
-    <row r="2" ht="25.05" customHeight="1" s="23">
-      <c r="A2" s="35" t="inlineStr">
-        <is>
-          <t>70 m³/gün Kapasiteli - Alıcı Ortama Deşarj</t>
-        </is>
-      </c>
-      <c r="C2" s="24" t="n"/>
-    </row>
-    <row r="3" ht="15.6" customHeight="1" s="23">
-      <c r="A3" s="33" t="inlineStr">
+    <row r="1" ht="18.6" customHeight="1" s="14" thickTop="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acme Endüstri A.Ş.	</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="12" t="n"/>
+    </row>
+    <row r="2" ht="25.05" customHeight="1" s="14">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>75,71 m³/gün Kapasiteli - Alıcı Ortama Deşarj</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="15.6" customHeight="1" s="14">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Dönen Biyolojik Disk Atıksu Arıtma Tesisi Teklifi</t>
         </is>
       </c>
-      <c r="C3" s="24" t="n"/>
+      <c r="C3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="18" t="n"/>
-    </row>
-    <row r="5" ht="15.6" customHeight="1" s="23">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="15.6" customHeight="1" s="14">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>PROJE DETAYLARI</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="C5" s="15" t="n"/>
+    </row>
+    <row r="6" ht="13.8" customFormat="1" customHeight="1" s="26">
+      <c r="A6" s="23" t="n"/>
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Hidrolik Yük</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>: 70 m³/gün</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>: 75,71 m³/gün</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="13.8" customFormat="1" customHeight="1" s="26">
+      <c r="A7" s="27" t="n"/>
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Organik Yük</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>: 24,50 kg/gün (70 m³/gün x 350 mg/l)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>: 22,71 kg/gün (75,71 m³/gün x 300 mg/l)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="13.8" customFormat="1" customHeight="1" s="26">
+      <c r="A8" s="27" t="n"/>
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Ön Arıtmada Giderilen Organik Yük</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>: 8,09 kg/gün ( 33% )</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>: 7,50 kg/gün ( 33% )</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="13.8" customFormat="1" customHeight="1" s="26">
+      <c r="A9" s="27" t="n"/>
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>PlanetDISK® Ünitesine Giren Organik Yük</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>: 16,42 kg/gün</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
+        <is>
+          <t>: 15,22 kg/gün</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="13.8" customFormat="1" customHeight="1" s="26">
+      <c r="A10" s="27" t="n"/>
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Atıksu Sıcaklığı</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>: Min 15°C-Maks 32°C</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="20" t="inlineStr">
+    <row r="11" ht="13.8" customFormat="1" customHeight="1" s="26">
+      <c r="A11" s="27" t="n"/>
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Kabul Edilen Atıksu Sıcaklığı</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="48" t="inlineStr">
         <is>
           <t>: 19 °C</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="20" t="inlineStr">
+    <row r="12" ht="13.8" customFormat="1" customHeight="1" s="26">
+      <c r="A12" s="27" t="n"/>
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Atıksuyun PlanetDISK® Ünitesinde Bekleme Süresi</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>: 1,54 saat (&gt;45 dakika minimum)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="15" t="n"/>
+      <c r="C12" s="48" t="inlineStr">
+        <is>
+          <t>: 1,43 saat (&gt;45 dakika minimum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="13.8" customFormat="1" customHeight="1" s="26">
+      <c r="A13" s="27" t="n"/>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="49" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="16" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="50" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="4" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="4" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Bu parametreler müşteri tarafından verilmiştir/ deneyimlerimiz ve literatür değerlerine göre seçilmiştir.</t>
         </is>
       </c>
-      <c r="C17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="15.6" customHeight="1" s="23">
-      <c r="A18" s="34" t="n"/>
+      <c r="C17" s="15" t="n"/>
+    </row>
+    <row r="18" ht="15.6" customHeight="1" s="14">
+      <c r="A18" s="19" t="n"/>
       <c r="C18" s="2" t="n"/>
     </row>
-    <row r="19" ht="15.6" customHeight="1" s="23">
-      <c r="A19" s="27" t="inlineStr">
+    <row r="19" ht="15.6" customHeight="1" s="14">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Atıksu Kaynağı</t>
         </is>
       </c>
-      <c r="C19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="78" customHeight="1" s="23">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="C19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="78" customHeight="1" s="14">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Tuvaletlerden ve her türlü tüketimden kaynaklanan evsel atıksular alınacaktır.
 Tesise yemekhanelerden kaynaklanan yağ içerikli atıksular yağ kapanından geçirilmeden alınmayacaktır. Ayrıca yağmur suyu girişi olmayacaktır.</t>
         </is>
       </c>
-      <c r="C20" s="24" t="n"/>
-    </row>
-    <row r="21" ht="15.6" customHeight="1" s="23">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="21" t="n"/>
+      <c r="C20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="15.6" customHeight="1" s="14">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="9" t="n"/>
       <c r="C21" s="2" t="n"/>
     </row>
-    <row r="22" ht="15.6" customHeight="1" s="23">
-      <c r="A22" s="27" t="inlineStr">
+    <row r="22" ht="15.6" customHeight="1" s="14">
+      <c r="A22" s="52" t="inlineStr">
         <is>
           <t>Önerilen Sistem</t>
         </is>
       </c>
-      <c r="C22" s="24" t="n"/>
-    </row>
-    <row r="23" ht="15.6" customHeight="1" s="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>· 1 adet PlanetDISK® MX 1 ünitesi (114 diskli) - Toplam 114 adet, 2,05 m çaplı disk, CTP (fiber) gövde.</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="n"/>
-    </row>
-    <row r="24" ht="15.6" customHeight="1" s="23">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>· TOPLAM YÜZEY ALANI: 114 disk x 6,6 m² x 1 adet = 752,4 m² yüzey alanı.</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="n"/>
-    </row>
-    <row r="25" ht="15.6" customHeight="1" s="23">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>· 1 adet LS 15 Lamella Seperatör Çökeltim Tankı, CTP (fiber) gövde.</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="n"/>
-    </row>
-    <row r="26" ht="15.6" customHeight="1" s="23">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>· TOPLAM 15 m² x 1 adet = 15 m² lamella yüzey alanı.</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="n"/>
-    </row>
-    <row r="27" ht="15.6" customHeight="1" s="23">
-      <c r="A27" s="25" t="n"/>
-      <c r="C27" s="24" t="n"/>
-    </row>
-    <row r="28" ht="15.6" customHeight="1" s="23">
-      <c r="A28" s="22" t="n"/>
-      <c r="C28" s="24" t="n"/>
-    </row>
-    <row r="29" ht="15.6" customHeight="1" s="23">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="21" t="n"/>
-      <c r="C29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="15.6" customHeight="1" s="23">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="C22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="15.6" customHeight="1" s="14">
+      <c r="A23" s="53" t="inlineStr">
+        <is>
+          <t>· 1 adet PlanetDISK® MX 1 ünitesi (112 diskli) - Toplam 112 adet, 2,05 m çaplı disk, CTP (fiber) gövde.</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="15.6" customHeight="1" s="14">
+      <c r="A24" s="53" t="inlineStr">
+        <is>
+          <t>· TOPLAM YÜZEY ALANI: 112 disk x 6,6 m² x 1 adet = 739,2 m² yüzey alanı.</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="15.6" customHeight="1" s="14">
+      <c r="A25" s="53" t="inlineStr">
+        <is>
+          <t>· 1 adet LS 30 Lamella Seperatör Çökeltim Tankı, CTP (fiber) gövde.</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="15.6" customHeight="1" s="14">
+      <c r="A26" s="53" t="inlineStr">
+        <is>
+          <t>· TOPLAM 30 m² x 1 adet = 30 m² lamella yüzey alanı.</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="15.6" customHeight="1" s="14">
+      <c r="A27" s="35" t="n"/>
+      <c r="C27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="15.6" customHeight="1" s="14">
+      <c r="A28" s="35" t="n"/>
+      <c r="C28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="15.6" customHeight="1" s="14">
+      <c r="A29" s="35" t="n"/>
+      <c r="C29" s="15" t="n"/>
+    </row>
+    <row r="30" ht="15.6" customHeight="1" s="14">
+      <c r="A30" s="36" t="n"/>
+      <c r="B30" s="37" t="n"/>
+      <c r="C30" s="38" t="n"/>
+    </row>
+    <row r="31" ht="15.6" customHeight="1" s="14">
+      <c r="A31" s="52" t="inlineStr">
         <is>
           <t>Disk Yüzey Alanı Hesaplaması</t>
         </is>
       </c>
-      <c r="C30" s="24" t="n"/>
-    </row>
-    <row r="31" ht="15.6" customHeight="1" s="23">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>π x r x r x 2 taraf x 114 disk -&gt; 3.14 x 1,025 x 1,025 x 2 x 114 = 752,2 m²</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="23" thickBot="1">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="8" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="23" thickTop="1"/>
+      <c r="C31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="15.6" customHeight="1" s="14">
+      <c r="A32" s="54" t="inlineStr">
+        <is>
+          <t>π x r x r x 2 taraf x 112 disk -&gt; 3.14 x 1,025 x 1,025 x 2 x 112 = 739,0 m²</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="14" thickBot="1">
+      <c r="A33" s="40" t="n"/>
+      <c r="B33" s="41" t="n"/>
+      <c r="C33" s="42" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="14" thickTop="1"/>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
